--- a/src/External/Agriculture.Seeding/Data/GardenData.xlsx
+++ b/src/External/Agriculture.Seeding/Data/GardenData.xlsx
@@ -5,13 +5,15 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Farms" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="FarmPlots" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="PlayerFarms" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Roles" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Users" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="27">
   <si>
     <t xml:space="preserve">UserName</t>
   </si>
@@ -71,6 +73,39 @@
   </si>
   <si>
     <t xml:space="preserve">IsActive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperAdmin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Has full access to the game system, including system configuration, player management, and game data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manages players, farms, game content, and general game operations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moderator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitors player activities and handles reports, inappropriate content, and player-related issues.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A player who owns and manages farms, grows crops, collects resources, and participates in game activities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PasswordHash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RoleName</t>
   </si>
 </sst>
 </file>
@@ -103,9 +138,11 @@
       <family val="0"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -150,7 +187,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -159,7 +196,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -331,8 +376,8 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="14.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="15.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -348,7 +393,7 @@
       <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -365,7 +410,7 @@
       <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -584,4 +629,116 @@
     <oddFooter>&amp;C&amp;"Times New Roman"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="89.71"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.7"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>123456</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>